--- a/KAMCHATKA_STATUS_2610.xlsx
+++ b/KAMCHATKA_STATUS_2610.xlsx
@@ -18,8 +18,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все позиции (315)'!$A$1:$R$316</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Брать'!$A$1:$R$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Брать при условии'!$A$1:$R$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Торг (бюджет)'!$A$1:$R$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Брать при условии'!$A$1:$R$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Торг (бюджет)'!$A$1:$R$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Заказать у других'!$A$1:$R$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Не отработано'!$A$1:$R$148</definedName>
   </definedNames>
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>142</v>
+        <v>280</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5465540.22</v>
+        <v>5499074.22</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>3293174.74</v>
+        <v>3324224.74</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>4912100</v>
+        <v>4939700</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>298</v>
+        <v>160</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2141226.36</v>
+        <v>2107692.36</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2516503.5</v>
+        <v>2478277.5</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1916900</v>
+        <v>1889300</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -799,12 +799,12 @@
         <v>22359287.69</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>18595773.85</v>
+        <v>18588597.85</v>
       </c>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>поставщик -16.8% к нашей цене</t>
+          <t>поставщик -16.9% к нашей цене</t>
         </is>
       </c>
     </row>
@@ -8439,20 +8439,20 @@
         </is>
       </c>
       <c r="C106" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>1.3/39</t>
+          <t>1.6/50</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
+          <t>Кран шаровой 11б27п(м) Ду 015 Ру16 3-х ходовой для манометров</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>243</v>
@@ -8468,256 +8468,250 @@
         <v>200</v>
       </c>
       <c r="L106" s="6" t="n">
+        <v>32076</v>
+      </c>
+      <c r="M106" s="6" t="n">
+        <v>29700</v>
+      </c>
+      <c r="N106" s="7" t="inlineStr">
+        <is>
+          <t>КИПИКА (прайс 01.10)</t>
+        </is>
+      </c>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровый трёхходовой для манометра 11б27пм.1 Ру16 Ду15 G1/2×M20×1,5 (арт. 021011011)</t>
+        </is>
+      </c>
+      <c r="P106" s="7" t="inlineStr">
+        <is>
+          <t>со склада, доставка ТК</t>
+        </is>
+      </c>
+      <c r="Q106" s="7" t="inlineStr">
+        <is>
+          <t>в наличии (письмо 27.10); подтвердить Т до +225 °C, полный проход, хромированная пробка, фторопласт-4; номер в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="R106" s="7" t="inlineStr">
+        <is>
+          <t>ООО «Пензапромарматура» +7 (8412) 909-200</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>Брать при условии</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>1.3/39</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>243</v>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="I107" s="18" t="n">
+        <v>-0.07407407407407407</v>
+      </c>
+      <c r="J107" s="6" t="n"/>
+      <c r="K107" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="L107" s="6" t="n">
         <v>8262</v>
       </c>
-      <c r="M106" s="6" t="n">
+      <c r="M107" s="6" t="n">
         <v>7650</v>
       </c>
-      <c r="N106" s="7" t="inlineStr">
+      <c r="N107" s="7" t="inlineStr">
         <is>
           <t>КИПИКА (прайс 01.10)</t>
         </is>
       </c>
-      <c r="O106" s="7" t="inlineStr">
-        <is>
-          <t>Кран трёхходовой для манометра с контр. фланцем 11б18бк(ф)2 Ру16 Ду15 G1/2×G1/2 с рукояткой (арт. 013011111) — пробковый</t>
-        </is>
-      </c>
-      <c r="P106" s="7" t="inlineStr">
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t>Кран трёхходовой для манометра с контр. фланцем 11б18бк(ф)1 Ру16 Ду15 G1/2×M20×1,5 с рукояткой (арт. 013011211)</t>
+        </is>
+      </c>
+      <c r="P107" s="7" t="inlineStr">
         <is>
           <t>со склада, доставка ТК</t>
         </is>
       </c>
-      <c r="Q106" s="7" t="inlineStr">
-        <is>
-          <t>ТЗ: латунь ЛЦ40Сд, пробка латунь + фторопласт, внутренняя резьба, длина 50 мм, Т −50…+150 — подтвердить по паспорту; от 51 шт — при общем заказе со 11б27пм</t>
-        </is>
-      </c>
-      <c r="R106" s="7" t="inlineStr">
+      <c r="Q107" s="7" t="inlineStr">
+        <is>
+          <t>в наличии (письмо 27.10); подтвердить длину 50 мм, Т −50…+150 °C; номер в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="R107" s="7" t="inlineStr">
         <is>
           <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «Пензапромарматура» +7 (8412) 909-200</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="40" customHeight="1">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>Торг: наш бюджет</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Задвижки</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>1.3/96</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Задвижка 30ч6бр Ду 150 Ру 10</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="G107" s="6" t="n">
-        <v>18572</v>
-      </c>
-      <c r="H107" s="6" t="n">
-        <v>22283.91</v>
-      </c>
-      <c r="I107" s="19" t="n">
-        <v>0.1998659272022398</v>
-      </c>
-      <c r="J107" s="6" t="n">
-        <v>22283.91</v>
-      </c>
-      <c r="K107" s="6" t="n">
-        <v>16700</v>
-      </c>
-      <c r="L107" s="6" t="n">
-        <v>352868</v>
-      </c>
-      <c r="M107" s="6" t="n">
-        <v>423394.29</v>
-      </c>
-      <c r="N107" s="7" t="inlineStr">
-        <is>
-          <t>ДН.РУ</t>
-        </is>
-      </c>
-      <c r="O107" s="7" t="inlineStr">
-        <is>
-          <t>Задвижка параллельная 30ч6бр DN.ru GVP1818M-2W-F-S Ду150 Ру10 фланцевая, материал корпуса - чугун СЧ20, материал диска -</t>
-        </is>
-      </c>
-      <c r="P107" s="7" t="inlineStr">
-        <is>
-          <t>склад Москва</t>
-        </is>
-      </c>
-      <c r="Q107" s="7" t="inlineStr">
-        <is>
-          <t>дороже на +20%</t>
-        </is>
-      </c>
-      <c r="R107" s="7" t="inlineStr">
-        <is>
-          <t>ООО «БК-Арматура» 8 (495) 925-51-64</t>
-        </is>
-      </c>
-    </row>
     <row r="108" ht="40" customHeight="1">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>Торг: наш бюджет</t>
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>Брать при условии</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Задвижки</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>1.6/42</t>
+          <t>1.3/100</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>Задвижка 30с41нж Ду 50 Ру 16</t>
+          <t>Кран 11б27п(м) Ду 15 Ру 16 3-х ходовой для манометров</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G108" s="6" t="n">
-        <v>7149</v>
+        <v>243</v>
       </c>
       <c r="H108" s="6" t="n">
-        <v>7955.62</v>
-      </c>
-      <c r="I108" s="19" t="n">
-        <v>0.1128297664008953</v>
-      </c>
-      <c r="J108" s="6" t="n">
-        <v>7955.62</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="I108" s="18" t="n">
+        <v>-0.07407407407407407</v>
+      </c>
+      <c r="J108" s="6" t="n"/>
       <c r="K108" s="6" t="n">
-        <v>6400</v>
+        <v>200</v>
       </c>
       <c r="L108" s="6" t="n">
-        <v>100086</v>
+        <v>972</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>111378.68</v>
+        <v>900</v>
       </c>
       <c r="N108" s="7" t="inlineStr">
         <is>
-          <t>ДН.РУ</t>
+          <t>КИПИКА (прайс 01.10)</t>
         </is>
       </c>
       <c r="O108" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клиновая 30с41нж DN.ru GVWR2121M-2W-F-S Ду50 Ру16 фланцевая, корпус - сталь 25Л, материал клина - 30-35 сталь 2</t>
+          <t>Кран шаровый трёхходовой для манометра 11б27пм.1 Ру16 Ду15 G1/2×M20×1,5 (арт. 021011011)</t>
         </is>
       </c>
       <c r="P108" s="7" t="inlineStr">
         <is>
-          <t>? раб.дн.</t>
+          <t>со склада, доставка ТК</t>
         </is>
       </c>
       <c r="Q108" s="7" t="inlineStr">
         <is>
-          <t>дороже на +11%</t>
+          <t>в наличии (письмо 27.10); подтвердить длину 50 мм, Т −50…+150 °C; номер в реестре МПТ</t>
         </is>
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>СИБЗТА 8-800-350-91-13; АО «Пензтяжпромарматура» 8-800-444-00-28 (продажи); АО НПО «Тяжпромарматура» +7 (495) 411-77-57; АО «Благовещенский арматурный завод» +7 (347) 662-99-10</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «Пензапромарматура» +7 (8412) 909-200</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>Торг: наш бюджет</t>
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>Брать при условии</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Задвижки</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>1.3/94</t>
+          <t>1.6/16</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Задвижка 30ч6бр Ду 80 Ру 10</t>
+          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>6387</v>
+        <v>243</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>8256.35</v>
-      </c>
-      <c r="I109" s="19" t="n">
-        <v>0.2926804446532019</v>
-      </c>
-      <c r="J109" s="6" t="n">
-        <v>8256.35</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="I109" s="18" t="n">
+        <v>-0.07407407407407407</v>
+      </c>
+      <c r="J109" s="6" t="n"/>
       <c r="K109" s="6" t="n">
-        <v>5700</v>
+        <v>200</v>
       </c>
       <c r="L109" s="6" t="n">
-        <v>89418</v>
+        <v>486</v>
       </c>
       <c r="M109" s="6" t="n">
-        <v>115588.9</v>
+        <v>450</v>
       </c>
       <c r="N109" s="7" t="inlineStr">
         <is>
-          <t>ДН.РУ</t>
+          <t>КИПИКА (прайс 01.10)</t>
         </is>
       </c>
       <c r="O109" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Задвижка параллельная 30ч6бр DN.ru GVP1818M-2W-F-S Ду80 Ру16 фланцевая, материал корпуса - чугун СЧ20, материал диска - </t>
+          <t>Кран шаровый трёхходовой для манометра 11б27пм.1 Ру16 Ду15 G1/2×M20×1,5 (арт. 021011011)</t>
         </is>
       </c>
       <c r="P109" s="7" t="inlineStr">
         <is>
-          <t>склад Москва</t>
+          <t>со склада, доставка ТК</t>
         </is>
       </c>
       <c r="Q109" s="7" t="inlineStr">
         <is>
-          <t>дороже на +29%</t>
+          <t>в наличии (письмо 27.10); подтвердить Т до +225 °C, полный проход, хромированная пробка, фторопласт-4; номер в реестре МПТ</t>
         </is>
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>ООО «БК-Арматура» 8 (495) 925-51-64</t>
+          <t>ООО «Пензапромарматура» +7 (8412) 909-200</t>
         </is>
       </c>
     </row>
@@ -8733,41 +8727,41 @@
         </is>
       </c>
       <c r="C110" s="5" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>1.1/7</t>
+          <t>1.3/96</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Задвижка 30с41нж Ду 50 Ру 16</t>
+          <t>Задвижка 30ч6бр Ду 150 Ру 10</t>
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G110" s="6" t="n">
-        <v>7149</v>
+        <v>18572</v>
       </c>
       <c r="H110" s="6" t="n">
-        <v>7955.62</v>
+        <v>22283.91</v>
       </c>
       <c r="I110" s="19" t="n">
-        <v>0.1128297664008953</v>
+        <v>0.1998659272022398</v>
       </c>
       <c r="J110" s="6" t="n">
-        <v>7955.62</v>
+        <v>22283.91</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>6400</v>
+        <v>16700</v>
       </c>
       <c r="L110" s="6" t="n">
-        <v>71490</v>
+        <v>352868</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>79556.2</v>
+        <v>423394.29</v>
       </c>
       <c r="N110" s="7" t="inlineStr">
         <is>
@@ -8776,22 +8770,22 @@
       </c>
       <c r="O110" s="7" t="inlineStr">
         <is>
-          <t>Задвижка клиновая 30с41нж DN.ru GVWR2121M-2W-F-S Ду50 Ру16 фланцевая, корпус - сталь 25Л, материал клина - 30-35 сталь 2</t>
+          <t>Задвижка параллельная 30ч6бр DN.ru GVP1818M-2W-F-S Ду150 Ру10 фланцевая, материал корпуса - чугун СЧ20, материал диска -</t>
         </is>
       </c>
       <c r="P110" s="7" t="inlineStr">
         <is>
-          <t>? раб.дн.</t>
+          <t>склад Москва</t>
         </is>
       </c>
       <c r="Q110" s="7" t="inlineStr">
         <is>
-          <t>дороже на +11%</t>
+          <t>дороже на +20%</t>
         </is>
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>СИБЗТА 8-800-350-91-13; АО «Пензтяжпромарматура» 8-800-444-00-28 (продажи); АО НПО «Тяжпромарматура» +7 (495) 411-77-57; АО «Благовещенский арматурный завод» +7 (347) 662-99-10</t>
+          <t>ООО «БК-Арматура» 8 (495) 925-51-64</t>
         </is>
       </c>
     </row>
@@ -8807,11 +8801,11 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>1.3/73</t>
+          <t>1.6/42</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -8820,7 +8814,7 @@
         </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G111" s="6" t="n">
         <v>7149</v>
@@ -8838,10 +8832,10 @@
         <v>6400</v>
       </c>
       <c r="L111" s="6" t="n">
-        <v>42894</v>
+        <v>100086</v>
       </c>
       <c r="M111" s="6" t="n">
-        <v>47733.72</v>
+        <v>111378.68</v>
       </c>
       <c r="N111" s="7" t="inlineStr">
         <is>
@@ -8881,11 +8875,11 @@
         </is>
       </c>
       <c r="C112" s="5" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>1.6/48</t>
+          <t>1.3/94</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
@@ -8894,7 +8888,7 @@
         </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>6387</v>
@@ -8912,10 +8906,10 @@
         <v>5700</v>
       </c>
       <c r="L112" s="6" t="n">
-        <v>19161</v>
+        <v>89418</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>24769.05</v>
+        <v>115588.9</v>
       </c>
       <c r="N112" s="7" t="inlineStr">
         <is>
@@ -8951,45 +8945,45 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Клапаны</t>
+          <t>Задвижки</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>1.3/55</t>
+          <t>1.1/7</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорны 15нж65нж Ду 100 Ру 16 фланцевый</t>
+          <t>Задвижка 30с41нж Ду 50 Ру 16</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>36554</v>
+        <v>7149</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>43183.12</v>
+        <v>7955.62</v>
       </c>
       <c r="I113" s="19" t="n">
-        <v>0.1813514252886141</v>
+        <v>0.1128297664008953</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>43183.12</v>
+        <v>7955.62</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>32800</v>
+        <v>6400</v>
       </c>
       <c r="L113" s="6" t="n">
-        <v>328986</v>
+        <v>71490</v>
       </c>
       <c r="M113" s="6" t="n">
-        <v>388648.08</v>
+        <v>79556.2</v>
       </c>
       <c r="N113" s="7" t="inlineStr">
         <is>
@@ -8998,22 +8992,22 @@
       </c>
       <c r="O113" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду100 Ру16 фланцевый, корпус - нержавеющая сталь 304, диск - нер</t>
+          <t>Задвижка клиновая 30с41нж DN.ru GVWR2121M-2W-F-S Ду50 Ру16 фланцевая, корпус - сталь 25Л, материал клина - 30-35 сталь 2</t>
         </is>
       </c>
       <c r="P113" s="7" t="inlineStr">
         <is>
-          <t>склад Москва</t>
+          <t>? раб.дн.</t>
         </is>
       </c>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>дороже на +18%</t>
+          <t>дороже на +11%</t>
         </is>
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
+          <t>СИБЗТА 8-800-350-91-13; АО «Пензтяжпромарматура» 8-800-444-00-28 (продажи); АО НПО «Тяжпромарматура» +7 (495) 411-77-57; АО «Благовещенский арматурный завод» +7 (347) 662-99-10</t>
         </is>
       </c>
     </row>
@@ -9025,45 +9019,45 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>Клапаны</t>
+          <t>Задвижки</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>1.3/11</t>
+          <t>1.3/73</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Регулятор давления РД-НО (Нормально открытый) Ду 50 Ру 16</t>
+          <t>Задвижка 30с41нж Ду 50 Ру 16</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G114" s="6" t="n">
-        <v>79717.24000000001</v>
+        <v>7149</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>89689.52</v>
+        <v>7955.62</v>
       </c>
       <c r="I114" s="19" t="n">
-        <v>0.1250956505769643</v>
+        <v>0.1128297664008953</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>89689.52</v>
+        <v>7955.62</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>71700</v>
+        <v>6400</v>
       </c>
       <c r="L114" s="6" t="n">
-        <v>239151.72</v>
+        <v>42894</v>
       </c>
       <c r="M114" s="6" t="n">
-        <v>269068.56</v>
+        <v>47733.72</v>
       </c>
       <c r="N114" s="7" t="inlineStr">
         <is>
@@ -9072,7 +9066,7 @@
       </c>
       <c r="O114" s="7" t="inlineStr">
         <is>
-          <t>Регулятор давления после себя Энерготехномаш УРРД-НО-РД Ду50 Ру16 фланцевый, Kvy - 32м3/ч, Tmax 150°С, уплотнение - EPDM</t>
+          <t>Задвижка клиновая 30с41нж DN.ru GVWR2121M-2W-F-S Ду50 Ру16 фланцевая, корпус - сталь 25Л, материал клина - 30-35 сталь 2</t>
         </is>
       </c>
       <c r="P114" s="7" t="inlineStr">
@@ -9082,12 +9076,12 @@
       </c>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>дороже на +13%</t>
+          <t>дороже на +11%</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>ООО «Ридан» +7 (495) 792-57-57; АО «Сафоновский завод «Теплоконтроль» 8-800-201-58-67; АО «Армагус» (49241) 2-32-41, 2-42-26; Теплосила 8-800-700-77-85</t>
+          <t>СИБЗТА 8-800-350-91-13; АО «Пензтяжпромарматура» 8-800-444-00-28 (продажи); АО НПО «Тяжпромарматура» +7 (495) 411-77-57; АО «Благовещенский арматурный завод» +7 (347) 662-99-10</t>
         </is>
       </c>
     </row>
@@ -9099,45 +9093,45 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Клапаны</t>
+          <t>Задвижки</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>1.3/9</t>
+          <t>1.6/48</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Регулятор давления РД-НО (Нормально открытый) Ду 25 Ру 16</t>
+          <t>Задвижка 30ч6бр Ду 80 Ру 10</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>58471.55</v>
+        <v>6387</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>73960.67</v>
+        <v>8256.35</v>
       </c>
       <c r="I115" s="19" t="n">
-        <v>0.2649001095404517</v>
+        <v>0.2926804446532019</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>73960.67</v>
+        <v>8256.35</v>
       </c>
       <c r="K115" s="6" t="n">
-        <v>52600</v>
+        <v>5700</v>
       </c>
       <c r="L115" s="6" t="n">
-        <v>116943.1</v>
+        <v>19161</v>
       </c>
       <c r="M115" s="6" t="n">
-        <v>147921.34</v>
+        <v>24769.05</v>
       </c>
       <c r="N115" s="7" t="inlineStr">
         <is>
@@ -9146,22 +9140,22 @@
       </c>
       <c r="O115" s="7" t="inlineStr">
         <is>
-          <t>Регулятор давления после себя Энерготехномаш УРРД-НО-РД Ду25 Ру16 фланцевый, Kvy - 3.2м3/ч, Tmax 150°С, уплотнение - EPD</t>
+          <t xml:space="preserve">Задвижка параллельная 30ч6бр DN.ru GVP1818M-2W-F-S Ду80 Ру16 фланцевая, материал корпуса - чугун СЧ20, материал диска - </t>
         </is>
       </c>
       <c r="P115" s="7" t="inlineStr">
         <is>
-          <t>? раб.дн.</t>
+          <t>склад Москва</t>
         </is>
       </c>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>дороже на +26%</t>
+          <t>дороже на +29%</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>ООО «Ридан» +7 (495) 792-57-57; АО «Сафоновский завод «Теплоконтроль» 8-800-201-58-67; АО «Армагус» (49241) 2-32-41, 2-42-26; Теплосила 8-800-700-77-85</t>
+          <t>ООО «БК-Арматура» 8 (495) 925-51-64</t>
         </is>
       </c>
     </row>
@@ -9177,41 +9171,41 @@
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>1.3/30</t>
+          <t>1.3/55</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный межфланцевый пружинный тарельчатый NVD-802R Ду 125 Ру 16</t>
+          <t>Клапан запорны 15нж65нж Ду 100 Ру 16 фланцевый</t>
         </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G116" s="6" t="n">
-        <v>58156</v>
+        <v>36554</v>
       </c>
       <c r="H116" s="6" t="n">
-        <v>71182.73</v>
+        <v>43183.12</v>
       </c>
       <c r="I116" s="19" t="n">
-        <v>0.2239963202421074</v>
+        <v>0.1813514252886141</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>71182.73</v>
+        <v>43183.12</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>52300</v>
+        <v>32800</v>
       </c>
       <c r="L116" s="6" t="n">
-        <v>116312</v>
+        <v>328986</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>142365.46</v>
+        <v>388648.08</v>
       </c>
       <c r="N116" s="7" t="inlineStr">
         <is>
@@ -9220,22 +9214,22 @@
       </c>
       <c r="O116" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный Ридан NVD-802R Ду125 Ру16 межфланцевый, пружинный, корпус - чугун, диск - сталь, уплотнение - 1 шт EPDM</t>
+          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду100 Ру16 фланцевый, корпус - нержавеющая сталь 304, диск - нер</t>
         </is>
       </c>
       <c r="P116" s="7" t="inlineStr">
         <is>
-          <t>1-2 раб.дн.</t>
+          <t>склад Москва</t>
         </is>
       </c>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>дороже на +22%</t>
+          <t>дороже на +18%</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
+          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
         </is>
       </c>
     </row>
@@ -9251,41 +9245,41 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>1.6/13</t>
+          <t>1.3/11</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранительный 17с6нж Ду 50 Ру 16</t>
+          <t>Регулятор давления РД-НО (Нормально открытый) Ду 50 Ру 16</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>36900.12</v>
+        <v>79717.24000000001</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>42031.44</v>
+        <v>89689.52</v>
       </c>
       <c r="I117" s="19" t="n">
-        <v>0.1390597103749256</v>
+        <v>0.1250956505769643</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>42031.44</v>
+        <v>89689.52</v>
       </c>
       <c r="K117" s="6" t="n">
-        <v>33200</v>
+        <v>71700</v>
       </c>
       <c r="L117" s="6" t="n">
-        <v>73800.24000000001</v>
+        <v>239151.72</v>
       </c>
       <c r="M117" s="6" t="n">
-        <v>84062.88</v>
+        <v>269068.56</v>
       </c>
       <c r="N117" s="7" t="inlineStr">
         <is>
@@ -9294,7 +9288,7 @@
       </c>
       <c r="O117" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранительный Авангард 17с6нж Ду50-80 Ру16 полноподъемный пружинный фланцевый, корпус - углеродистая сталь 25</t>
+          <t>Регулятор давления после себя Энерготехномаш УРРД-НО-РД Ду50 Ру16 фланцевый, Kvy - 32м3/ч, Tmax 150°С, уплотнение - EPDM</t>
         </is>
       </c>
       <c r="P117" s="7" t="inlineStr">
@@ -9304,12 +9298,12 @@
       </c>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>дороже на +14%</t>
+          <t>дороже на +13%</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «ПИК-Алгрупп» 8-800-200-52-76; АО «Благовещенский арматурный завод» +7 (347) 662-99-10</t>
+          <t>ООО «Ридан» +7 (495) 792-57-57; АО «Сафоновский завод «Теплоконтроль» 8-800-201-58-67; АО «Армагус» (49241) 2-32-41, 2-42-26; Теплосила 8-800-700-77-85</t>
         </is>
       </c>
     </row>
@@ -9325,41 +9319,41 @@
         </is>
       </c>
       <c r="C118" s="5" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>1.6/12</t>
+          <t>1.3/9</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранительный 17с28нж Ду 50 Ру16 (Рн 10-16)</t>
+          <t>Регулятор давления РД-НО (Нормально открытый) Ду 25 Ру 16</t>
         </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G118" s="6" t="n">
-        <v>22754.83</v>
+        <v>58471.55</v>
       </c>
       <c r="H118" s="6" t="n">
-        <v>28309.49</v>
+        <v>73960.67</v>
       </c>
       <c r="I118" s="19" t="n">
-        <v>0.2441090528911884</v>
+        <v>0.2649001095404517</v>
       </c>
       <c r="J118" s="6" t="n">
-        <v>28309.49</v>
+        <v>73960.67</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>20400</v>
+        <v>52600</v>
       </c>
       <c r="L118" s="6" t="n">
-        <v>68264.49000000001</v>
+        <v>116943.1</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>84928.47</v>
+        <v>147921.34</v>
       </c>
       <c r="N118" s="7" t="inlineStr">
         <is>
@@ -9368,7 +9362,7 @@
       </c>
       <c r="O118" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранительный Авангард 17с28нж Ду50-80 Ру16-6 полноподъемный пружинный 1 шт фланцевый</t>
+          <t>Регулятор давления после себя Энерготехномаш УРРД-НО-РД Ду25 Ру16 фланцевый, Kvy - 3.2м3/ч, Tmax 150°С, уплотнение - EPD</t>
         </is>
       </c>
       <c r="P118" s="7" t="inlineStr">
@@ -9378,12 +9372,12 @@
       </c>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>дороже на +24%</t>
+          <t>дороже на +26%</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «ПИК-Алгрупп» 8-800-200-52-76; АО «Благовещенский арматурный завод» +7 (347) 662-99-10</t>
+          <t>ООО «Ридан» +7 (495) 792-57-57; АО «Сафоновский завод «Теплоконтроль» 8-800-201-58-67; АО «Армагус» (49241) 2-32-41, 2-42-26; Теплосила 8-800-700-77-85</t>
         </is>
       </c>
     </row>
@@ -9399,41 +9393,41 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>1.3/59</t>
+          <t>1.3/30</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорны 15нж65нж Ду 50 Ру 16 фланцевый</t>
+          <t>Клапан обратный межфланцевый пружинный тарельчатый NVD-802R Ду 125 Ру 16</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>16762</v>
+        <v>58156</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>18714.8</v>
+        <v>71182.73</v>
       </c>
       <c r="I119" s="19" t="n">
-        <v>0.1165016107863024</v>
+        <v>0.2239963202421074</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>18714.8</v>
+        <v>71182.73</v>
       </c>
       <c r="K119" s="6" t="n">
-        <v>15000</v>
+        <v>52300</v>
       </c>
       <c r="L119" s="6" t="n">
-        <v>67048</v>
+        <v>116312</v>
       </c>
       <c r="M119" s="6" t="n">
-        <v>74859.2</v>
+        <v>142365.46</v>
       </c>
       <c r="N119" s="7" t="inlineStr">
         <is>
@@ -9442,22 +9436,22 @@
       </c>
       <c r="O119" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду50 Ру16 фланцевый, корпус - нержавеющая На складе в сталь 304,</t>
+          <t>Клапан обратный Ридан NVD-802R Ду125 Ру16 межфланцевый, пружинный, корпус - чугун, диск - сталь, уплотнение - 1 шт EPDM</t>
         </is>
       </c>
       <c r="P119" s="7" t="inlineStr">
         <is>
-          <t>склад Москва</t>
+          <t>1-2 раб.дн.</t>
         </is>
       </c>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>дороже на +12%</t>
+          <t>дороже на +22%</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
+          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
         </is>
       </c>
     </row>
@@ -9473,41 +9467,41 @@
         </is>
       </c>
       <c r="C120" s="5" t="n">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>1.3/54</t>
+          <t>1.6/13</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорны 15нж65нж Ду 80 Ру 16 фланцевый</t>
+          <t>Клапан предохранительный 17с6нж Ду 50 Ру 16</t>
         </is>
       </c>
       <c r="F120" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G120" s="6" t="n">
-        <v>28880</v>
+        <v>36900.12</v>
       </c>
       <c r="H120" s="6" t="n">
-        <v>33625.64</v>
+        <v>42031.44</v>
       </c>
       <c r="I120" s="19" t="n">
-        <v>0.1643227146814403</v>
+        <v>0.1390597103749256</v>
       </c>
       <c r="J120" s="6" t="n">
-        <v>33625.64</v>
+        <v>42031.44</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>25900</v>
+        <v>33200</v>
       </c>
       <c r="L120" s="6" t="n">
-        <v>57760</v>
+        <v>73800.24000000001</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>67251.28</v>
+        <v>84062.88</v>
       </c>
       <c r="N120" s="7" t="inlineStr">
         <is>
@@ -9516,7 +9510,7 @@
       </c>
       <c r="O120" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду80 Ру16 фланцевый, корпус - нержавеющая сталь 304, диск - нерж</t>
+          <t>Клапан предохранительный Авангард 17с6нж Ду50-80 Ру16 полноподъемный пружинный фланцевый, корпус - углеродистая сталь 25</t>
         </is>
       </c>
       <c r="P120" s="7" t="inlineStr">
@@ -9526,12 +9520,12 @@
       </c>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>дороже на +16%</t>
+          <t>дороже на +14%</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
+          <t>ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «ПИК-Алгрупп» 8-800-200-52-76; АО «Благовещенский арматурный завод» +7 (347) 662-99-10</t>
         </is>
       </c>
     </row>
@@ -9547,41 +9541,41 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>1.6/14</t>
+          <t>1.6/12</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранительный 17с6нж Ду 80 Ру 16</t>
+          <t>Клапан предохранительный 17с28нж Ду 50 Ру16 (Рн 10-16)</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>54119.81</v>
+        <v>22754.83</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>62429.84</v>
+        <v>28309.49</v>
       </c>
       <c r="I121" s="19" t="n">
-        <v>0.1535487652303287</v>
+        <v>0.2441090528911884</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>62429.84</v>
+        <v>28309.49</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>48700</v>
+        <v>20400</v>
       </c>
       <c r="L121" s="6" t="n">
-        <v>54119.81</v>
+        <v>68264.49000000001</v>
       </c>
       <c r="M121" s="6" t="n">
-        <v>62429.84</v>
+        <v>84928.47</v>
       </c>
       <c r="N121" s="7" t="inlineStr">
         <is>
@@ -9590,7 +9584,7 @@
       </c>
       <c r="O121" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранительный Авангард 17с6нж Ду80-100 Ру16 полноподъемный пружинный фланцевый, корпус - 25 -30 раб. углероди</t>
+          <t>Клапан предохранительный Авангард 17с28нж Ду50-80 Ру16-6 полноподъемный пружинный 1 шт фланцевый</t>
         </is>
       </c>
       <c r="P121" s="7" t="inlineStr">
@@ -9600,7 +9594,7 @@
       </c>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>дороже на +15%</t>
+          <t>дороже на +24%</t>
         </is>
       </c>
       <c r="R121" s="7" t="inlineStr">
@@ -9621,20 +9615,20 @@
         </is>
       </c>
       <c r="C122" s="5" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>1.1/3</t>
+          <t>1.3/59</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный15нж65нж Ду 50 Ру 16</t>
+          <t>Клапан запорны 15нж65нж Ду 50 Ру 16 фланцевый</t>
         </is>
       </c>
       <c r="F122" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>16762</v>
@@ -9652,10 +9646,10 @@
         <v>15000</v>
       </c>
       <c r="L122" s="6" t="n">
-        <v>50286</v>
+        <v>67048</v>
       </c>
       <c r="M122" s="6" t="n">
-        <v>56144.39999999999</v>
+        <v>74859.2</v>
       </c>
       <c r="N122" s="7" t="inlineStr">
         <is>
@@ -9695,41 +9689,41 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>1.6/23</t>
+          <t>1.3/54</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный 15кч16п1 Ду 50 Ру 25</t>
+          <t>Клапан запорны 15нж65нж Ду 80 Ру 16 фланцевый</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G123" s="6" t="n">
-        <v>7471</v>
+        <v>28880</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>8464.969999999999</v>
+        <v>33625.64</v>
       </c>
       <c r="I123" s="19" t="n">
-        <v>0.1330437692410653</v>
+        <v>0.1643227146814403</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>8464.969999999999</v>
+        <v>33625.64</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>6700</v>
+        <v>25900</v>
       </c>
       <c r="L123" s="6" t="n">
-        <v>37355</v>
+        <v>57760</v>
       </c>
       <c r="M123" s="6" t="n">
-        <v>42324.85</v>
+        <v>67251.28</v>
       </c>
       <c r="N123" s="7" t="inlineStr">
         <is>
@@ -9738,17 +9732,17 @@
       </c>
       <c r="O123" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный Луидор 15кч16п1 Ду50 Ру25 чугунный, фланцевый, штурвал</t>
+          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду80 Ру16 фланцевый, корпус - нержавеющая сталь 304, диск - нерж</t>
         </is>
       </c>
       <c r="P123" s="7" t="inlineStr">
         <is>
-          <t>1-2 раб.дн.</t>
+          <t>? раб.дн.</t>
         </is>
       </c>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>дороже на +13%</t>
+          <t>дороже на +16%</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
@@ -9769,41 +9763,41 @@
         </is>
       </c>
       <c r="C124" s="5" t="n">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>1.6/21</t>
+          <t>1.6/14</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный 15кч16п1 Ду 32 Ру 25</t>
+          <t>Клапан предохранительный 17с6нж Ду 80 Ру 16</t>
         </is>
       </c>
       <c r="F124" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G124" s="6" t="n">
-        <v>5292</v>
+        <v>54119.81</v>
       </c>
       <c r="H124" s="6" t="n">
-        <v>5996.91</v>
+        <v>62429.84</v>
       </c>
       <c r="I124" s="19" t="n">
-        <v>0.133202947845805</v>
+        <v>0.1535487652303287</v>
       </c>
       <c r="J124" s="6" t="n">
-        <v>5996.91</v>
+        <v>62429.84</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>4700</v>
+        <v>48700</v>
       </c>
       <c r="L124" s="6" t="n">
-        <v>37044</v>
+        <v>54119.81</v>
       </c>
       <c r="M124" s="6" t="n">
-        <v>41978.37</v>
+        <v>62429.84</v>
       </c>
       <c r="N124" s="7" t="inlineStr">
         <is>
@@ -9812,22 +9806,22 @@
       </c>
       <c r="O124" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный Луидор 15кч16п1 Ду32 Ру25 чугунный, фланцевый, штурвал</t>
+          <t>Клапан предохранительный Авангард 17с6нж Ду80-100 Ру16 полноподъемный пружинный фланцевый, корпус - 25 -30 раб. углероди</t>
         </is>
       </c>
       <c r="P124" s="7" t="inlineStr">
         <is>
-          <t>1-2 раб.дн.</t>
+          <t>? раб.дн.</t>
         </is>
       </c>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>дороже на +13%</t>
+          <t>дороже на +15%</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
+          <t>ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «ПИК-Алгрупп» 8-800-200-52-76; АО «Благовещенский арматурный завод» +7 (347) 662-99-10</t>
         </is>
       </c>
     </row>
@@ -9843,41 +9837,41 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>1.6/27</t>
+          <t>1.1/3</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный 15нж65нж Ду 100 Ру 16</t>
+          <t>Клапан запорный15нж65нж Ду 50 Ру 16</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G125" s="6" t="n">
-        <v>36554</v>
+        <v>16762</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>43183.12</v>
+        <v>18714.8</v>
       </c>
       <c r="I125" s="19" t="n">
-        <v>0.1813514252886141</v>
+        <v>0.1165016107863024</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>43183.12</v>
+        <v>18714.8</v>
       </c>
       <c r="K125" s="6" t="n">
-        <v>32800</v>
+        <v>15000</v>
       </c>
       <c r="L125" s="6" t="n">
-        <v>36554</v>
+        <v>50286</v>
       </c>
       <c r="M125" s="6" t="n">
-        <v>43183.12</v>
+        <v>56144.39999999999</v>
       </c>
       <c r="N125" s="7" t="inlineStr">
         <is>
@@ -9886,7 +9880,7 @@
       </c>
       <c r="O125" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду100 Ру16 фланцевый, корпус - нержавеющая На складе в сталь 304</t>
+          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду50 Ру16 фланцевый, корпус - нержавеющая На складе в сталь 304,</t>
         </is>
       </c>
       <c r="P125" s="7" t="inlineStr">
@@ -9896,7 +9890,7 @@
       </c>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>дороже на +18%</t>
+          <t>дороже на +12%</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
@@ -9917,41 +9911,41 @@
         </is>
       </c>
       <c r="C126" s="5" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>1.6/26</t>
+          <t>1.6/23</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный 15нж65нж Ду 80 Ру 16</t>
+          <t>Клапан запорный 15кч16п1 Ду 50 Ру 25</t>
         </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G126" s="6" t="n">
-        <v>28880</v>
+        <v>7471</v>
       </c>
       <c r="H126" s="6" t="n">
-        <v>33625.64</v>
+        <v>8464.969999999999</v>
       </c>
       <c r="I126" s="19" t="n">
-        <v>0.1643227146814403</v>
+        <v>0.1330437692410653</v>
       </c>
       <c r="J126" s="6" t="n">
-        <v>33625.64</v>
+        <v>8464.969999999999</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>25900</v>
+        <v>6700</v>
       </c>
       <c r="L126" s="6" t="n">
-        <v>28880</v>
+        <v>37355</v>
       </c>
       <c r="M126" s="6" t="n">
-        <v>33625.64</v>
+        <v>42324.85</v>
       </c>
       <c r="N126" s="7" t="inlineStr">
         <is>
@@ -9960,17 +9954,17 @@
       </c>
       <c r="O126" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду80 Ру16 фланцевый, корпус - нержавеющая сталь 304, диск - нерж</t>
+          <t>Клапан запорный Луидор 15кч16п1 Ду50 Ру25 чугунный, фланцевый, штурвал</t>
         </is>
       </c>
       <c r="P126" s="7" t="inlineStr">
         <is>
-          <t>? раб.дн.</t>
+          <t>1-2 раб.дн.</t>
         </is>
       </c>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>дороже на +16%</t>
+          <t>дороже на +13%</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
@@ -9991,41 +9985,41 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>1.3/18</t>
+          <t>1.6/21</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный межфланцевый 19ч21бр Ду 80 Ру 16</t>
+          <t>Клапан запорный 15кч16п1 Ду 32 Ру 25</t>
         </is>
       </c>
       <c r="F127" s="5" t="n">
         <v>7</v>
       </c>
       <c r="G127" s="6" t="n">
-        <v>2834</v>
+        <v>5292</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>3219.58</v>
+        <v>5996.91</v>
       </c>
       <c r="I127" s="19" t="n">
-        <v>0.1360550458715597</v>
+        <v>0.133202947845805</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>3219.58</v>
+        <v>5996.91</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>2500</v>
+        <v>4700</v>
       </c>
       <c r="L127" s="6" t="n">
-        <v>19838</v>
+        <v>37044</v>
       </c>
       <c r="M127" s="6" t="n">
-        <v>22537.06</v>
+        <v>41978.37</v>
       </c>
       <c r="N127" s="7" t="inlineStr">
         <is>
@@ -10034,7 +10028,7 @@
       </c>
       <c r="O127" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный ЛМЗ 19Ч21БР Ду80 Ру16 поворотный, межфланцевый, материал - чугун, диск - чугун</t>
+          <t>Клапан запорный Луидор 15кч16п1 Ду32 Ру25 чугунный, фланцевый, штурвал</t>
         </is>
       </c>
       <c r="P127" s="7" t="inlineStr">
@@ -10044,12 +10038,12 @@
       </c>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>дороже на +14%</t>
+          <t>дороже на +13%</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
+          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
         </is>
       </c>
     </row>
@@ -10065,41 +10059,41 @@
         </is>
       </c>
       <c r="C128" s="5" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>1.3/25</t>
+          <t>1.6/27</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный 16ч42р Ду 100 Ру 2,5</t>
+          <t>Клапан запорный 15нж65нж Ду 100 Ру 16</t>
         </is>
       </c>
       <c r="F128" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G128" s="6" t="n">
-        <v>6199</v>
+        <v>36554</v>
       </c>
       <c r="H128" s="6" t="n">
-        <v>7205.32</v>
+        <v>43183.12</v>
       </c>
       <c r="I128" s="19" t="n">
-        <v>0.162335860622681</v>
+        <v>0.1813514252886141</v>
       </c>
       <c r="J128" s="6" t="n">
-        <v>7205.32</v>
+        <v>43183.12</v>
       </c>
       <c r="K128" s="6" t="n">
-        <v>5500</v>
+        <v>32800</v>
       </c>
       <c r="L128" s="6" t="n">
-        <v>18597</v>
+        <v>36554</v>
       </c>
       <c r="M128" s="6" t="n">
-        <v>21615.96</v>
+        <v>43183.12</v>
       </c>
       <c r="N128" s="7" t="inlineStr">
         <is>
@@ -10108,22 +10102,22 @@
       </c>
       <c r="O128" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный Луидор 16ч42р Ду100 Ру2.5 фланцевый, приемный, с приемной сеткой, корпус - чугун, диск - 1 шт чугун, упл</t>
+          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду100 Ру16 фланцевый, корпус - нержавеющая На складе в сталь 304</t>
         </is>
       </c>
       <c r="P128" s="7" t="inlineStr">
         <is>
-          <t>1-2 раб.дн.</t>
+          <t>склад Москва</t>
         </is>
       </c>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>дороже на +16%</t>
+          <t>дороже на +18%</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
+          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
         </is>
       </c>
     </row>
@@ -10139,41 +10133,41 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>1.3/16</t>
+          <t>1.6/26</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный межфланцевый 19ч21бр Ду 100 Ру 16</t>
+          <t>Клапан запорный 15нж65нж Ду 80 Ру 16</t>
         </is>
       </c>
       <c r="F129" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>3807</v>
+        <v>28880</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>4404.81</v>
+        <v>33625.64</v>
       </c>
       <c r="I129" s="19" t="n">
-        <v>0.1570291568163911</v>
+        <v>0.1643227146814403</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>4404.81</v>
+        <v>33625.64</v>
       </c>
       <c r="K129" s="6" t="n">
-        <v>3400</v>
+        <v>25900</v>
       </c>
       <c r="L129" s="6" t="n">
-        <v>15228</v>
+        <v>28880</v>
       </c>
       <c r="M129" s="6" t="n">
-        <v>17619.24</v>
+        <v>33625.64</v>
       </c>
       <c r="N129" s="7" t="inlineStr">
         <is>
@@ -10182,12 +10176,12 @@
       </c>
       <c r="O129" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный ЛМЗ 19Ч21БР Ду100 Ру16 поворотный, межфланцевый, материал - чугун, диск - чугун</t>
+          <t>Клапан запорный сальниковый 15нж65нж DN.ru VSO3131M-F-S Ду80 Ру16 фланцевый, корпус - нержавеющая сталь 304, диск - нерж</t>
         </is>
       </c>
       <c r="P129" s="7" t="inlineStr">
         <is>
-          <t>1-2 раб.дн.</t>
+          <t>? раб.дн.</t>
         </is>
       </c>
       <c r="Q129" s="7" t="inlineStr">
@@ -10197,7 +10191,7 @@
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
+          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
         </is>
       </c>
     </row>
@@ -10213,41 +10207,41 @@
         </is>
       </c>
       <c r="C130" s="5" t="n">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>1.3/53</t>
+          <t>1.3/18</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный 15б1п Ду 50 Ру16</t>
+          <t>Клапан обратный межфланцевый 19ч21бр Ду 80 Ру 16</t>
         </is>
       </c>
       <c r="F130" s="5" t="n">
         <v>7</v>
       </c>
       <c r="G130" s="6" t="n">
-        <v>2049</v>
+        <v>2834</v>
       </c>
       <c r="H130" s="6" t="n">
-        <v>2331.42</v>
+        <v>3219.58</v>
       </c>
       <c r="I130" s="19" t="n">
-        <v>0.1378330893118596</v>
+        <v>0.1360550458715597</v>
       </c>
       <c r="J130" s="6" t="n">
-        <v>2331.42</v>
+        <v>3219.58</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="L130" s="6" t="n">
-        <v>14343</v>
+        <v>19838</v>
       </c>
       <c r="M130" s="6" t="n">
-        <v>16319.94</v>
+        <v>22537.06</v>
       </c>
       <c r="N130" s="7" t="inlineStr">
         <is>
@@ -10256,7 +10250,7 @@
       </c>
       <c r="O130" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный SantechSystems 15Б1П SV101 Ду50 Ру16 латунный, резьбовой, внутренняя резьба, прямой</t>
+          <t>Клапан обратный ЛМЗ 19Ч21БР Ду80 Ру16 поворотный, межфланцевый, материал - чугун, диск - чугун</t>
         </is>
       </c>
       <c r="P130" s="7" t="inlineStr">
@@ -10271,7 +10265,7 @@
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
+          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
         </is>
       </c>
     </row>
@@ -10287,41 +10281,41 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>1.3/64</t>
+          <t>1.3/25</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный 15ч75п2 Ду 25 Ру10</t>
+          <t>Клапан обратный 16ч42р Ду 100 Ру 2,5</t>
         </is>
       </c>
       <c r="F131" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G131" s="6" t="n">
-        <v>4000</v>
+        <v>6199</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>4427.99</v>
+        <v>7205.32</v>
       </c>
       <c r="I131" s="19" t="n">
-        <v>0.1069974999999999</v>
+        <v>0.162335860622681</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>4427.99</v>
+        <v>7205.32</v>
       </c>
       <c r="K131" s="6" t="n">
-        <v>3600</v>
+        <v>5500</v>
       </c>
       <c r="L131" s="6" t="n">
-        <v>12000</v>
+        <v>18597</v>
       </c>
       <c r="M131" s="6" t="n">
-        <v>13283.97</v>
+        <v>21615.96</v>
       </c>
       <c r="N131" s="7" t="inlineStr">
         <is>
@@ -10330,22 +10324,22 @@
       </c>
       <c r="O131" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Клапан запорный сальниковый DN.ru VSO1121M-F-S Ду25 Ру16, фланцевый, На складе в корпус - чугун GG25, уплотнение - 1 шт </t>
+          <t>Клапан обратный Луидор 16ч42р Ду100 Ру2.5 фланцевый, приемный, с приемной сеткой, корпус - чугун, диск - 1 шт чугун, упл</t>
         </is>
       </c>
       <c r="P131" s="7" t="inlineStr">
         <is>
-          <t>склад Москва</t>
+          <t>1-2 раб.дн.</t>
         </is>
       </c>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>дороже на +11%</t>
+          <t>дороже на +16%</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
+          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
         </is>
       </c>
     </row>
@@ -10361,41 +10355,41 @@
         </is>
       </c>
       <c r="C132" s="5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>1.3/17</t>
+          <t>1.3/16</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный межфланцевый 19ч21бр Ду 50 Ру 16</t>
+          <t>Клапан обратный межфланцевый 19ч21бр Ду 100 Ру 16</t>
         </is>
       </c>
       <c r="F132" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G132" s="6" t="n">
-        <v>1910</v>
+        <v>3807</v>
       </c>
       <c r="H132" s="6" t="n">
-        <v>2194.78</v>
+        <v>4404.81</v>
       </c>
       <c r="I132" s="19" t="n">
-        <v>0.1490994764397906</v>
+        <v>0.1570291568163911</v>
       </c>
       <c r="J132" s="6" t="n">
-        <v>2194.78</v>
+        <v>4404.81</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>1700</v>
+        <v>3400</v>
       </c>
       <c r="L132" s="6" t="n">
-        <v>11460</v>
+        <v>15228</v>
       </c>
       <c r="M132" s="6" t="n">
-        <v>13168.68</v>
+        <v>17619.24</v>
       </c>
       <c r="N132" s="7" t="inlineStr">
         <is>
@@ -10404,7 +10398,7 @@
       </c>
       <c r="O132" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный ЛМЗ 19Ч21БР Ду50 Ру16 поворотный, межфланцевый, материал - чугун, диск - чугун</t>
+          <t>Клапан обратный ЛМЗ 19Ч21БР Ду100 Ру16 поворотный, межфланцевый, материал - чугун, диск - чугун</t>
         </is>
       </c>
       <c r="P132" s="7" t="inlineStr">
@@ -10414,7 +10408,7 @@
       </c>
       <c r="Q132" s="7" t="inlineStr">
         <is>
-          <t>дороже на +15%</t>
+          <t>дороже на +16%</t>
         </is>
       </c>
       <c r="R132" s="7" t="inlineStr">
@@ -10435,41 +10429,41 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>1.3/51</t>
+          <t>1.3/53</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный 15б1п Ду 32 Ру16</t>
+          <t>Клапан запорный 15б1п Ду 50 Ру16</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G133" s="6" t="n">
-        <v>875</v>
+        <v>2049</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>1028.46</v>
+        <v>2331.42</v>
       </c>
       <c r="I133" s="19" t="n">
-        <v>0.1753828571428573</v>
+        <v>0.1378330893118596</v>
       </c>
       <c r="J133" s="6" t="n">
-        <v>1028.46</v>
+        <v>2331.42</v>
       </c>
       <c r="K133" s="6" t="n">
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="L133" s="6" t="n">
-        <v>8750</v>
+        <v>14343</v>
       </c>
       <c r="M133" s="6" t="n">
-        <v>10284.6</v>
+        <v>16319.94</v>
       </c>
       <c r="N133" s="7" t="inlineStr">
         <is>
@@ -10478,7 +10472,7 @@
       </c>
       <c r="O133" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный SantechSystems 15Б1П Ду32 Ру16 латунный, резьбовой, внутренняя резьба, прямой</t>
+          <t>Клапан запорный SantechSystems 15Б1П SV101 Ду50 Ру16 латунный, резьбовой, внутренняя резьба, прямой</t>
         </is>
       </c>
       <c r="P133" s="7" t="inlineStr">
@@ -10488,7 +10482,7 @@
       </c>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>дороже на +18%</t>
+          <t>дороже на +14%</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
@@ -10509,41 +10503,41 @@
         </is>
       </c>
       <c r="C134" s="5" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>1.3/52</t>
+          <t>1.3/64</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный 15б1п Ду 40 Ру16</t>
+          <t>Клапан запорный 15ч75п2 Ду 25 Ру10</t>
         </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G134" s="6" t="n">
-        <v>1534</v>
+        <v>4000</v>
       </c>
       <c r="H134" s="6" t="n">
-        <v>1731.18</v>
+        <v>4427.99</v>
       </c>
       <c r="I134" s="19" t="n">
-        <v>0.1285397653194265</v>
+        <v>0.1069974999999999</v>
       </c>
       <c r="J134" s="6" t="n">
-        <v>1731.18</v>
+        <v>4427.99</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>1300</v>
+        <v>3600</v>
       </c>
       <c r="L134" s="6" t="n">
-        <v>7670</v>
+        <v>12000</v>
       </c>
       <c r="M134" s="6" t="n">
-        <v>8655.9</v>
+        <v>13283.97</v>
       </c>
       <c r="N134" s="7" t="inlineStr">
         <is>
@@ -10552,17 +10546,17 @@
       </c>
       <c r="O134" s="7" t="inlineStr">
         <is>
-          <t>Клапан запорный Цветлит 15б1п 1 1/2" Ду40 Ру16 латунный, внутренняя резьба, штурвал</t>
+          <t xml:space="preserve">Клапан запорный сальниковый DN.ru VSO1121M-F-S Ду25 Ру16, фланцевый, На складе в корпус - чугун GG25, уплотнение - 1 шт </t>
         </is>
       </c>
       <c r="P134" s="7" t="inlineStr">
         <is>
-          <t>1-2 раб.дн.</t>
+          <t>склад Москва</t>
         </is>
       </c>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>дороже на +13%</t>
+          <t>дороже на +11%</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
@@ -10583,41 +10577,41 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>1.6/6</t>
+          <t>1.3/17</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный межфланцевый 19ч21бр Ду 80 Ру 16</t>
+          <t>Клапан обратный межфланцевый 19ч21бр Ду 50 Ру 16</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G135" s="6" t="n">
-        <v>2834</v>
+        <v>1910</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>3351.34</v>
+        <v>2194.78</v>
       </c>
       <c r="I135" s="19" t="n">
-        <v>0.1825476358503881</v>
+        <v>0.1490994764397906</v>
       </c>
       <c r="J135" s="6" t="n">
-        <v>3351.34</v>
+        <v>2194.78</v>
       </c>
       <c r="K135" s="6" t="n">
-        <v>2500</v>
+        <v>1700</v>
       </c>
       <c r="L135" s="6" t="n">
-        <v>5668</v>
+        <v>11460</v>
       </c>
       <c r="M135" s="6" t="n">
-        <v>6702.68</v>
+        <v>13168.68</v>
       </c>
       <c r="N135" s="7" t="inlineStr">
         <is>
@@ -10626,7 +10620,7 @@
       </c>
       <c r="O135" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Клапан обратный Мегастрой 19ч21бр Ду80 Ру16 межфланцевый, одностворчатый, корпус - чугун, диск - 1 шт чугун, уплотнение </t>
+          <t>Клапан обратный ЛМЗ 19Ч21БР Ду50 Ру16 поворотный, межфланцевый, материал - чугун, диск - чугун</t>
         </is>
       </c>
       <c r="P135" s="7" t="inlineStr">
@@ -10636,7 +10630,7 @@
       </c>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>дороже на +18%</t>
+          <t>дороже на +15%</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
@@ -10657,41 +10651,41 @@
         </is>
       </c>
       <c r="C136" s="5" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>1.6/4</t>
+          <t>1.3/51</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный межфланцевый 19ч21бр Ду 100 Ру 16</t>
+          <t>Клапан запорный 15б1п Ду 32 Ру16</t>
         </is>
       </c>
       <c r="F136" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G136" s="6" t="n">
-        <v>3807</v>
+        <v>875</v>
       </c>
       <c r="H136" s="6" t="n">
-        <v>4596.35</v>
+        <v>1028.46</v>
       </c>
       <c r="I136" s="19" t="n">
-        <v>0.2073417389020227</v>
+        <v>0.1753828571428573</v>
       </c>
       <c r="J136" s="6" t="n">
-        <v>4596.35</v>
+        <v>1028.46</v>
       </c>
       <c r="K136" s="6" t="n">
-        <v>3400</v>
+        <v>700</v>
       </c>
       <c r="L136" s="6" t="n">
-        <v>3807</v>
+        <v>8750</v>
       </c>
       <c r="M136" s="6" t="n">
-        <v>4596.35</v>
+        <v>10284.6</v>
       </c>
       <c r="N136" s="7" t="inlineStr">
         <is>
@@ -10700,22 +10694,22 @@
       </c>
       <c r="O136" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный Мегастрой 19ч21бр Ду100 Ру16 межфланцевый, одностворчатый, корпус - чугун, диск - 1 шт чугун, уплотнение</t>
+          <t>Клапан запорный SantechSystems 15Б1П Ду32 Ру16 латунный, резьбовой, внутренняя резьба, прямой</t>
         </is>
       </c>
       <c r="P136" s="7" t="inlineStr">
         <is>
-          <t>2-3 раб.дн.</t>
+          <t>1-2 раб.дн.</t>
         </is>
       </c>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>дороже на +21%</t>
+          <t>дороже на +18%</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
+          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
         </is>
       </c>
     </row>
@@ -10731,41 +10725,41 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>1.6/5</t>
+          <t>1.3/52</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>Клапан обратный межфланцевый 19ч21бр Ду 50 Ру 16</t>
+          <t>Клапан запорный 15б1п Ду 40 Ру16</t>
         </is>
       </c>
       <c r="F137" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G137" s="6" t="n">
-        <v>1910</v>
+        <v>1534</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>2280.79</v>
+        <v>1731.18</v>
       </c>
       <c r="I137" s="19" t="n">
-        <v>0.194130890052356</v>
+        <v>0.1285397653194265</v>
       </c>
       <c r="J137" s="6" t="n">
-        <v>2280.79</v>
+        <v>1731.18</v>
       </c>
       <c r="K137" s="6" t="n">
-        <v>1700</v>
+        <v>1300</v>
       </c>
       <c r="L137" s="6" t="n">
-        <v>1910</v>
+        <v>7670</v>
       </c>
       <c r="M137" s="6" t="n">
-        <v>2280.79</v>
+        <v>8655.9</v>
       </c>
       <c r="N137" s="7" t="inlineStr">
         <is>
@@ -10774,7 +10768,7 @@
       </c>
       <c r="O137" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Клапан обратный Мегастрой 19ч21бр Ду50 Ру16 межфланцевый, одностворчатый, корпус - чугун, диск - 1 шт чугун, уплотнение </t>
+          <t>Клапан запорный Цветлит 15б1п 1 1/2" Ду40 Ру16 латунный, внутренняя резьба, штурвал</t>
         </is>
       </c>
       <c r="P137" s="7" t="inlineStr">
@@ -10784,12 +10778,12 @@
       </c>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>дороже на +19%</t>
+          <t>дороже на +13%</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
+          <t>АО «Благовещенский арматурный завод» +7 (347) 662-99-10; ООО «Победа-30» +7 (812) 458-55-97</t>
         </is>
       </c>
     </row>
@@ -10801,67 +10795,69 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Клапаны</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>1.6/50</t>
+          <t>1.6/6</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой 11б27п(м) Ду 015 Ру16 3-х ходовой для манометров</t>
+          <t>Клапан обратный межфланцевый 19ч21бр Ду 80 Ру 16</t>
         </is>
       </c>
       <c r="F138" s="5" t="n">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="G138" s="6" t="n">
-        <v>243</v>
+        <v>2834</v>
       </c>
       <c r="H138" s="6" t="n">
-        <v>277</v>
+        <v>3351.34</v>
       </c>
       <c r="I138" s="19" t="n">
-        <v>0.1399176954732511</v>
-      </c>
-      <c r="J138" s="6" t="n"/>
+        <v>0.1825476358503881</v>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>3351.34</v>
+      </c>
       <c r="K138" s="6" t="n">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="L138" s="6" t="n">
-        <v>32076</v>
+        <v>5668</v>
       </c>
       <c r="M138" s="6" t="n">
-        <v>36564</v>
+        <v>6702.68</v>
       </c>
       <c r="N138" s="7" t="inlineStr">
         <is>
-          <t>КИПИКА (прайс 01.10)</t>
+          <t>ДН.РУ</t>
         </is>
       </c>
       <c r="O138" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровый трёхходовой для манометра 11б27пм.2 Ру16 Ду15 G1/2×G1/2 (арт. 021011111)</t>
+          <t xml:space="preserve">Клапан обратный Мегастрой 19ч21бр Ду80 Ру16 межфланцевый, одностворчатый, корпус - чугун, диск - 1 шт чугун, уплотнение </t>
         </is>
       </c>
       <c r="P138" s="7" t="inlineStr">
         <is>
-          <t>со склада, доставка ТК</t>
+          <t>1-2 раб.дн.</t>
         </is>
       </c>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>дороже на +14%</t>
+          <t>дороже на +18%</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>ООО «Пензапромарматура» +7 (8412) 909-200</t>
+          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
         </is>
       </c>
     </row>
@@ -10873,67 +10869,69 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Клапаны</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>1.3/100</t>
+          <t>1.6/4</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>Кран 11б27п(м) Ду 15 Ру 16 3-х ходовой для манометров</t>
+          <t>Клапан обратный межфланцевый 19ч21бр Ду 100 Ру 16</t>
         </is>
       </c>
       <c r="F139" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G139" s="6" t="n">
-        <v>243</v>
+        <v>3807</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>277</v>
+        <v>4596.35</v>
       </c>
       <c r="I139" s="19" t="n">
-        <v>0.1399176954732511</v>
-      </c>
-      <c r="J139" s="6" t="n"/>
+        <v>0.2073417389020227</v>
+      </c>
+      <c r="J139" s="6" t="n">
+        <v>4596.35</v>
+      </c>
       <c r="K139" s="6" t="n">
-        <v>200</v>
+        <v>3400</v>
       </c>
       <c r="L139" s="6" t="n">
-        <v>972</v>
+        <v>3807</v>
       </c>
       <c r="M139" s="6" t="n">
-        <v>1108</v>
+        <v>4596.35</v>
       </c>
       <c r="N139" s="7" t="inlineStr">
         <is>
-          <t>КИПИКА (прайс 01.10)</t>
+          <t>ДН.РУ</t>
         </is>
       </c>
       <c r="O139" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровый трёхходовой для манометра 11б27пм.2 Ру16 Ду15 G1/2×G1/2 (арт. 021011111)</t>
+          <t>Клапан обратный Мегастрой 19ч21бр Ду100 Ру16 межфланцевый, одностворчатый, корпус - чугун, диск - 1 шт чугун, уплотнение</t>
         </is>
       </c>
       <c r="P139" s="7" t="inlineStr">
         <is>
-          <t>со склада, доставка ТК</t>
+          <t>2-3 раб.дн.</t>
         </is>
       </c>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>дороже на +14%</t>
+          <t>дороже на +21%</t>
         </is>
       </c>
       <c r="R139" s="7" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «Пензапромарматура» +7 (8412) 909-200</t>
+          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
         </is>
       </c>
     </row>
@@ -10945,67 +10943,69 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Клапаны</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>1.6/16</t>
+          <t>1.6/5</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
+          <t>Клапан обратный межфланцевый 19ч21бр Ду 50 Ру 16</t>
         </is>
       </c>
       <c r="F140" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G140" s="6" t="n">
-        <v>243</v>
+        <v>1910</v>
       </c>
       <c r="H140" s="6" t="n">
-        <v>277</v>
+        <v>2280.79</v>
       </c>
       <c r="I140" s="19" t="n">
-        <v>0.1399176954732511</v>
-      </c>
-      <c r="J140" s="6" t="n"/>
+        <v>0.194130890052356</v>
+      </c>
+      <c r="J140" s="6" t="n">
+        <v>2280.79</v>
+      </c>
       <c r="K140" s="6" t="n">
-        <v>200</v>
+        <v>1700</v>
       </c>
       <c r="L140" s="6" t="n">
-        <v>486</v>
+        <v>1910</v>
       </c>
       <c r="M140" s="6" t="n">
-        <v>554</v>
+        <v>2280.79</v>
       </c>
       <c r="N140" s="7" t="inlineStr">
         <is>
-          <t>КИПИКА (прайс 01.10)</t>
+          <t>ДН.РУ</t>
         </is>
       </c>
       <c r="O140" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровый трёхходовой для манометра 11б27пм.2 Ру16 Ду15 G1/2×G1/2 (арт. 021011111)</t>
+          <t xml:space="preserve">Клапан обратный Мегастрой 19ч21бр Ду50 Ру16 межфланцевый, одностворчатый, корпус - чугун, диск - 1 шт чугун, уплотнение </t>
         </is>
       </c>
       <c r="P140" s="7" t="inlineStr">
         <is>
-          <t>со склада, доставка ТК</t>
+          <t>1-2 раб.дн.</t>
         </is>
       </c>
       <c r="Q140" s="7" t="inlineStr">
         <is>
-          <t>дороже на +14%</t>
+          <t>дороже на +19%</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>ООО «Пензапромарматура» +7 (8412) 909-200</t>
+          <t>ООО «Ридан» +7 (495) 792-57-57; ООО «Торговый Дом АДЛ» +7 (495) 937-89-68; ООО «Победа-30» +7 (812) 458-55-97; АО «Армагус» (49241) 2-32-41, 2-42-26</t>
         </is>
       </c>
     </row>
@@ -25792,7 +25792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -28727,20 +28727,20 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>1.3/39</t>
+          <t>1.6/50</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
+          <t>Кран шаровой 11б27п(м) Ду 015 Ру16 3-х ходовой для манометров</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>243</v>
@@ -28756,39 +28756,255 @@
         <v>200</v>
       </c>
       <c r="L40" s="6" t="n">
+        <v>32076</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>29700</v>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>КИПИКА (прайс 01.10)</t>
+        </is>
+      </c>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровый трёхходовой для манометра 11б27пм.1 Ру16 Ду15 G1/2×M20×1,5 (арт. 021011011)</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>со склада, доставка ТК</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>в наличии (письмо 27.10); подтвердить Т до +225 °C, полный проход, хромированная пробка, фторопласт-4; номер в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="R40" s="7" t="inlineStr">
+        <is>
+          <t>ООО «Пензапромарматура» +7 (8412) 909-200</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Брать при условии</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>1.3/39</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>243</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>-0.07407407407407407</v>
+      </c>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="L41" s="6" t="n">
         <v>8262</v>
       </c>
-      <c r="M40" s="6" t="n">
+      <c r="M41" s="6" t="n">
         <v>7650</v>
       </c>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="N41" s="7" t="inlineStr">
         <is>
           <t>КИПИКА (прайс 01.10)</t>
         </is>
       </c>
-      <c r="O40" s="7" t="inlineStr">
-        <is>
-          <t>Кран трёхходовой для манометра с контр. фланцем 11б18бк(ф)2 Ру16 Ду15 G1/2×G1/2 с рукояткой (арт. 013011111) — пробковый</t>
-        </is>
-      </c>
-      <c r="P40" s="7" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>Кран трёхходовой для манометра с контр. фланцем 11б18бк(ф)1 Ру16 Ду15 G1/2×M20×1,5 с рукояткой (арт. 013011211)</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
         <is>
           <t>со склада, доставка ТК</t>
         </is>
       </c>
-      <c r="Q40" s="7" t="inlineStr">
-        <is>
-          <t>ТЗ: латунь ЛЦ40Сд, пробка латунь + фторопласт, внутренняя резьба, длина 50 мм, Т −50…+150 — подтвердить по паспорту; от 51 шт — при общем заказе со 11б27пм</t>
-        </is>
-      </c>
-      <c r="R40" s="7" t="inlineStr">
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>в наличии (письмо 27.10); подтвердить длину 50 мм, Т −50…+150 °C; номер в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="R41" s="7" t="inlineStr">
         <is>
           <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «Пензапромарматура» +7 (8412) 909-200</t>
         </is>
       </c>
     </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Брать при условии</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>1.3/100</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Кран 11б27п(м) Ду 15 Ру 16 3-х ходовой для манометров</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>243</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>-0.07407407407407407</v>
+      </c>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>972</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>КИПИКА (прайс 01.10)</t>
+        </is>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровый трёхходовой для манометра 11б27пм.1 Ру16 Ду15 G1/2×M20×1,5 (арт. 021011011)</t>
+        </is>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>со склада, доставка ТК</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>в наличии (письмо 27.10); подтвердить длину 50 мм, Т −50…+150 °C; номер в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="R42" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «Пензапромарматура» +7 (8412) 909-200</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Брать при условии</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>1.6/16</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>243</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="I43" s="18" t="n">
+        <v>-0.07407407407407407</v>
+      </c>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>486</v>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>КИПИКА (прайс 01.10)</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровый трёхходовой для манометра 11б27пм.1 Ру16 Ду15 G1/2×M20×1,5 (арт. 021011011)</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>со склада, доставка ТК</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>в наличии (письмо 27.10); подтвердить Т до +225 °C, полный проход, хромированная пробка, фторопласт-4; номер в реестре МПТ</t>
+        </is>
+      </c>
+      <c r="R43" s="7" t="inlineStr">
+        <is>
+          <t>ООО «Пензапромарматура» +7 (8412) 909-200</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R40"/>
+  <autoFilter ref="A1:R43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -28800,7 +29016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -31209,224 +31425,8 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Торг: наш бюджет</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Краны</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>1.6/50</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой 11б27п(м) Ду 015 Ру16 3-х ходовой для манометров</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>243</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>277</v>
-      </c>
-      <c r="I33" s="19" t="n">
-        <v>0.1399176954732511</v>
-      </c>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="L33" s="6" t="n">
-        <v>32076</v>
-      </c>
-      <c r="M33" s="6" t="n">
-        <v>36564</v>
-      </c>
-      <c r="N33" s="7" t="inlineStr">
-        <is>
-          <t>КИПИКА (прайс 01.10)</t>
-        </is>
-      </c>
-      <c r="O33" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровый трёхходовой для манометра 11б27пм.2 Ру16 Ду15 G1/2×G1/2 (арт. 021011111)</t>
-        </is>
-      </c>
-      <c r="P33" s="7" t="inlineStr">
-        <is>
-          <t>со склада, доставка ТК</t>
-        </is>
-      </c>
-      <c r="Q33" s="7" t="inlineStr">
-        <is>
-          <t>дороже на +14%</t>
-        </is>
-      </c>
-      <c r="R33" s="7" t="inlineStr">
-        <is>
-          <t>ООО «Пензапромарматура» +7 (8412) 909-200</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Торг: наш бюджет</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Краны</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>1.3/100</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Кран 11б27п(м) Ду 15 Ру 16 3-х ходовой для манометров</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>243</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>277</v>
-      </c>
-      <c r="I34" s="19" t="n">
-        <v>0.1399176954732511</v>
-      </c>
-      <c r="J34" s="6" t="n"/>
-      <c r="K34" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="L34" s="6" t="n">
-        <v>972</v>
-      </c>
-      <c r="M34" s="6" t="n">
-        <v>1108</v>
-      </c>
-      <c r="N34" s="7" t="inlineStr">
-        <is>
-          <t>КИПИКА (прайс 01.10)</t>
-        </is>
-      </c>
-      <c r="O34" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровый трёхходовой для манометра 11б27пм.2 Ру16 Ду15 G1/2×G1/2 (арт. 021011111)</t>
-        </is>
-      </c>
-      <c r="P34" s="7" t="inlineStr">
-        <is>
-          <t>со склада, доставка ТК</t>
-        </is>
-      </c>
-      <c r="Q34" s="7" t="inlineStr">
-        <is>
-          <t>дороже на +14%</t>
-        </is>
-      </c>
-      <c r="R34" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «Пензапромарматура» +7 (8412) 909-200</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Торг: наш бюджет</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Краны</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>1.6/16</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Кран для манометра трехходовой Ду 15 Ру 16</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="6" t="n">
-        <v>243</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>277</v>
-      </c>
-      <c r="I35" s="19" t="n">
-        <v>0.1399176954732511</v>
-      </c>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="L35" s="6" t="n">
-        <v>486</v>
-      </c>
-      <c r="M35" s="6" t="n">
-        <v>554</v>
-      </c>
-      <c r="N35" s="7" t="inlineStr">
-        <is>
-          <t>КИПИКА (прайс 01.10)</t>
-        </is>
-      </c>
-      <c r="O35" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровый трёхходовой для манометра 11б27пм.2 Ру16 Ду15 G1/2×G1/2 (арт. 021011111)</t>
-        </is>
-      </c>
-      <c r="P35" s="7" t="inlineStr">
-        <is>
-          <t>со склада, доставка ТК</t>
-        </is>
-      </c>
-      <c r="Q35" s="7" t="inlineStr">
-        <is>
-          <t>дороже на +14%</t>
-        </is>
-      </c>
-      <c r="R35" s="7" t="inlineStr">
-        <is>
-          <t>ООО «Пензапромарматура» +7 (8412) 909-200</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R35"/>
+  <autoFilter ref="A1:R32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
